--- a/moduli_aziende/aifecs/moduli_compilati/MOD-400-B-Parti_Interessate.xlsx
+++ b/moduli_aziende/aifecs/moduli_compilati/MOD-400-B-Parti_Interessate.xlsx
@@ -2,26 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb6e9411a694a45e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7f777444e84845f4"/>
   </x:sheets>
 </x:workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:authors>
-    <x:author/>
-  </x:authors>
-  <x:commentList>
-    <x:comment ref="A1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>AIFECS — BOZZA DA CONFERMARE. Proposta operativa per il sistema qualità ISO 9001. Ruoli, priorità, criteri e obiettivi sono proposte. I registri vanno compilati con dati ed evidenze reali. Vedere la guida e la proposta operativa del pacchetto.</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-  </x:commentList>
-</x:comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -370,9 +353,7 @@
       <x:c r="E2" s="9" t="str">
         <x:v>Da valutare</x:v>
       </x:c>
-      <x:c r="F2" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="F2" s="9"/>
     </x:row>
     <x:row r="3" ht="68" customHeight="1">
       <x:c r="A3" s="8" t="str">
@@ -388,9 +369,7 @@
       <x:c r="E3" s="9" t="str">
         <x:v>Da valutare</x:v>
       </x:c>
-      <x:c r="F3" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="F3" s="9"/>
     </x:row>
     <x:row r="4" ht="50" customHeight="1">
       <x:c r="A4" s="8" t="str">
@@ -406,9 +385,7 @@
       <x:c r="E4" s="9" t="str">
         <x:v>Da valutare</x:v>
       </x:c>
-      <x:c r="F4" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="F4" s="9"/>
     </x:row>
     <x:row r="5" ht="68" customHeight="1">
       <x:c r="A5" s="8" t="str">
@@ -424,9 +401,7 @@
       <x:c r="E5" s="9" t="str">
         <x:v>Da valutare</x:v>
       </x:c>
-      <x:c r="F5" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="F5" s="9"/>
     </x:row>
     <x:row r="6" ht="68" customHeight="1">
       <x:c r="A6" s="8" t="str">
@@ -442,9 +417,7 @@
       <x:c r="E6" s="9" t="str">
         <x:v>Da valutare</x:v>
       </x:c>
-      <x:c r="F6" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="F6" s="9"/>
     </x:row>
     <x:row r="7" ht="68" customHeight="1">
       <x:c r="A7" s="8" t="str">
@@ -460,9 +433,7 @@
       <x:c r="E7" s="9" t="str">
         <x:v>Da valutare</x:v>
       </x:c>
-      <x:c r="F7" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="F7" s="9"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="8" t="str">
@@ -478,9 +449,7 @@
       <x:c r="E8" s="9" t="str">
         <x:v>Da valutare</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="F8" s="9"/>
     </x:row>
     <x:row r="9" ht="50" customHeight="1">
       <x:c r="A9" s="8" t="str">
@@ -496,9 +465,7 @@
       <x:c r="E9" s="9" t="str">
         <x:v>Da valutare</x:v>
       </x:c>
-      <x:c r="F9" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="F9" s="9"/>
     </x:row>
     <x:row r="10" ht="50" customHeight="1">
       <x:c r="A10" s="8" t="str">
@@ -514,9 +481,7 @@
       <x:c r="E10" s="9" t="str">
         <x:v>Da valutare</x:v>
       </x:c>
-      <x:c r="F10" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="F10" s="9"/>
     </x:row>
     <x:row r="11" ht="50" customHeight="1">
       <x:c r="A11" s="8" t="str">
@@ -532,9 +497,7 @@
       <x:c r="E11" s="9" t="str">
         <x:v>Da valutare</x:v>
       </x:c>
-      <x:c r="F11" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="F11" s="9"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="8" t="str">
@@ -550,9 +513,7 @@
       <x:c r="E12" s="9" t="str">
         <x:v>Da valutare</x:v>
       </x:c>
-      <x:c r="F12" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="F12" s="9"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="8" t="str">
@@ -568,9 +529,7 @@
       <x:c r="E13" s="9" t="str">
         <x:v>Da valutare</x:v>
       </x:c>
-      <x:c r="F13" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="F13" s="9"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="8" t="str">
@@ -586,9 +545,7 @@
       <x:c r="E14" s="9" t="str">
         <x:v>Da valutare</x:v>
       </x:c>
-      <x:c r="F14" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="F14" s="9"/>
     </x:row>
     <x:row r="15" ht="68" customHeight="1">
       <x:c r="A15" s="8" t="str">
@@ -604,9 +561,7 @@
       <x:c r="E15" s="9" t="str">
         <x:v>Da valutare</x:v>
       </x:c>
-      <x:c r="F15" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="F15" s="9"/>
     </x:row>
     <x:row r="16" ht="68" customHeight="1">
       <x:c r="A16" s="8" t="str">
@@ -622,9 +577,7 @@
       <x:c r="E16" s="9" t="str">
         <x:v>Da valutare</x:v>
       </x:c>
-      <x:c r="F16" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="F16" s="9"/>
     </x:row>
     <x:row r="17" ht="50" customHeight="1">
       <x:c r="A17" s="8" t="str">
@@ -640,9 +593,7 @@
       <x:c r="E17" s="9" t="str">
         <x:v>Da valutare</x:v>
       </x:c>
-      <x:c r="F17" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="F17" s="9"/>
     </x:row>
     <x:row r="18" ht="68" customHeight="1">
       <x:c r="A18" s="8" t="str">
@@ -658,9 +609,7 @@
       <x:c r="E18" s="9" t="str">
         <x:v>Da valutare</x:v>
       </x:c>
-      <x:c r="F18" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="F18" s="9"/>
     </x:row>
     <x:row r="19" ht="51" customHeight="1">
       <x:c r="A19" s="2"/>
@@ -856,6 +805,5 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48b70cf6a4de4b7c"/>
 </x:worksheet>
 </file>